--- a/Lab_stuff/Course_materials/BTC181-LabTechniques/Attachments/VG008 Attachment - Sequence Reaction Master Mix Sheet.xlsx
+++ b/Lab_stuff/Course_materials/BTC181-LabTechniques/Attachments/VG008 Attachment - Sequence Reaction Master Mix Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\BL6PEPF000102CD\EXCELCNV\aee0a346-2b82-4bb6-9cd7-86e68f909bba\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="8_{F639D4A9-6A08-42A2-9E0F-67149FC70C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5819CA0-68C3-4CCA-8087-36B36293EAA1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73B02BA5-173F-4A9C-B067-45D7D2014242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,12 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
-  <si>
-    <t>Performed by (print, initial, and date):</t>
-  </si>
-  <si>
-    <t>Witnessed by (print, intial and date):</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
+  <si>
+    <t>Sanger Sequencing Batch Document</t>
+  </si>
+  <si>
+    <t>Performed by (print, initial, and date): _________________________</t>
+  </si>
+  <si>
+    <t>Witnessed by (print, intial and date): _________________________</t>
   </si>
   <si>
     <t>Tube #</t>
@@ -175,13 +178,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -348,17 +356,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -501,11 +498,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -547,10 +557,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
@@ -571,51 +581,52 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -941,7 +952,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
@@ -954,123 +965,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="60">
-      <c r="A3" s="1" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:14" ht="60">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="M5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2" t="s">
+      <c r="N5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="4">
-        <v>4</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4">
-        <f>SUM(C5:L5)</f>
-        <v>10</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1078,45 +1043,62 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="N6" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4">
+        <f>SUM(C7:L7)</f>
+        <v>10</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1133,13 +1115,13 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="12"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1150,14 +1132,14 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="11"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1167,14 +1149,14 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="11"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -1184,14 +1166,14 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="5"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
@@ -1201,14 +1183,14 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -1218,13 +1200,13 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="24"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -1235,7 +1217,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1250,9 +1232,9 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:13">
       <c r="A17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1267,9 +1249,9 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:13">
       <c r="A18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1284,9 +1266,9 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:13">
       <c r="A19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1301,9 +1283,9 @@
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:13">
       <c r="A20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1318,9 +1300,9 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:13">
       <c r="A21">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1335,15 +1317,15 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:13">
       <c r="A22">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -1352,16 +1334,16 @@
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:13">
       <c r="A23">
-        <v>17</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="11"/>
+        <v>15</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
@@ -1369,16 +1351,16 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:13">
       <c r="A24">
-        <v>18</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
@@ -1386,9 +1368,9 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:13">
       <c r="A25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="13"/>
@@ -1403,9 +1385,9 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:13">
       <c r="A26">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="13"/>
@@ -1420,9 +1402,9 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:13">
       <c r="A27">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="13"/>
@@ -1437,9 +1419,9 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:13">
       <c r="A28">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="13"/>
@@ -1454,15 +1436,15 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:13">
       <c r="A29">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B29" s="10"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
       <c r="G29" s="11"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
@@ -1471,25 +1453,15 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:13">
       <c r="A30">
-        <v>24</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="13">
-        <v>4</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="13">
-        <v>4</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>25</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
       <c r="G30" s="11"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -1498,142 +1470,138 @@
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
     </row>
-    <row r="32" spans="1:14" ht="42" customHeight="1">
-      <c r="A32" s="31" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31">
+        <v>23</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32">
+        <v>24</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="13">
+        <v>4</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="13">
+        <v>4</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="34" t="s">
+      <c r="G32" s="11"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+    </row>
+    <row r="34" spans="1:14" ht="36" customHeight="1">
+      <c r="A34" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="N32" s="35"/>
-    </row>
-    <row r="33" spans="1:14" ht="24">
-      <c r="A33" s="18" t="b">
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" s="37"/>
+    </row>
+    <row r="35" spans="1:14" ht="24">
+      <c r="A35" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="B33" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="17" t="s">
+      <c r="B35" s="34" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="24">
-      <c r="A34" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="24">
-      <c r="A35" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="N35" s="15" t="s">
-        <v>29</v>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="24">
       <c r="A36" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="B36" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="27"/>
+      <c r="B36" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N36" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="24">
       <c r="A37" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="B37" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="27"/>
+      <c r="B37" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="34"/>
       <c r="M37" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="24">
@@ -1641,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -1654,10 +1622,10 @@
       <c r="K38" s="26"/>
       <c r="L38" s="27"/>
       <c r="M38" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N38" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="24">
@@ -1665,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -1678,10 +1646,10 @@
       <c r="K39" s="26"/>
       <c r="L39" s="27"/>
       <c r="M39" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="24">
@@ -1689,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
@@ -1702,10 +1670,10 @@
       <c r="K40" s="26"/>
       <c r="L40" s="27"/>
       <c r="M40" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N40" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="24">
@@ -1713,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -1726,10 +1694,10 @@
       <c r="K41" s="26"/>
       <c r="L41" s="27"/>
       <c r="M41" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="24">
@@ -1737,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
@@ -1750,10 +1718,10 @@
       <c r="K42" s="26"/>
       <c r="L42" s="27"/>
       <c r="M42" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N42" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="21" customHeight="1">
@@ -1761,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -1774,64 +1742,99 @@
       <c r="K43" s="26"/>
       <c r="L43" s="27"/>
       <c r="M43" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="24">
-      <c r="A44" s="20" t="b">
+      <c r="A44" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="N44" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A45" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="B45" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="N44" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A45" t="s">
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="27"/>
+      <c r="M45" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="N45" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="24">
+      <c r="A46" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="B46" s="28" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" t="s">
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
         <v>42</v>
       </c>
     </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="B33:L33"/>
-    <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B35:L35"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B43:L43"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B44:L44"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B37:L37"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B39:L39"/>
-    <mergeCell ref="B41:L41"/>
+  <mergeCells count="1">
+    <mergeCell ref="M34:N34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToWidth="0" orientation="landscape"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>